--- a/Slump_ML_Results_v2.xlsx
+++ b/Slump_ML_Results_v2.xlsx
@@ -17412,7 +17412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19608,10 +19608,1909 @@
         <v>58.9637</v>
       </c>
     </row>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B143" s="4" t="n">
+        <v>67.94799999999999</v>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>5.948</v>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>190.845</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>-29.155</v>
+      </c>
+      <c r="I143" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J143" s="4" t="n">
+        <v>200.564</v>
+      </c>
+      <c r="K143" s="4" t="n">
+        <v>10.564</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="B144" s="6" t="n">
+        <v>559.4349999999999</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>9.435</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>158.403</v>
+      </c>
+      <c r="G144" s="6" t="n">
+        <v>-11.597</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>177.52</v>
+      </c>
+      <c r="K144" s="6" t="n">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>580</v>
+      </c>
+      <c r="B145" s="4" t="n">
+        <v>585.643</v>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>5.643</v>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>156.469</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="I145" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J145" s="4" t="n">
+        <v>150.037</v>
+      </c>
+      <c r="K145" s="4" t="n">
+        <v>-9.962999999999999</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="B146" s="6" t="n">
+        <v>202.048</v>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>22.048</v>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>206.711</v>
+      </c>
+      <c r="G146" s="6" t="n">
+        <v>-78.289</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>129.115</v>
+      </c>
+      <c r="K146" s="6" t="n">
+        <v>-0.885</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B147" s="4" t="n">
+        <v>175.535</v>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>-9.465</v>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>152.231</v>
+      </c>
+      <c r="G147" s="4" t="n">
+        <v>-7.769</v>
+      </c>
+      <c r="I147" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J147" s="4" t="n">
+        <v>189.595</v>
+      </c>
+      <c r="K147" s="4" t="n">
+        <v>-20.405</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>251.688</v>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>-23.312</v>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v>127.026</v>
+      </c>
+      <c r="G148" s="6" t="n">
+        <v>67.026</v>
+      </c>
+      <c r="I148" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J148" s="6" t="n">
+        <v>186.908</v>
+      </c>
+      <c r="K148" s="6" t="n">
+        <v>6.908</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B149" s="4" t="n">
+        <v>182.374</v>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>-7.626</v>
+      </c>
+      <c r="E149" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>170.469</v>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>-4.531</v>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v>163.499</v>
+      </c>
+      <c r="K149" s="4" t="n">
+        <v>3.499</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>247.755</v>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>-17.245</v>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>190.616</v>
+      </c>
+      <c r="G150" s="6" t="n">
+        <v>-24.384</v>
+      </c>
+      <c r="I150" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J150" s="6" t="n">
+        <v>132.809</v>
+      </c>
+      <c r="K150" s="6" t="n">
+        <v>2.809</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B151" s="4" t="n">
+        <v>638.258</v>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>-11.742</v>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>105.328</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>-14.672</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>203.757</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>-6.243</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>52.398</v>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>12.398</v>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F152" s="6" t="n">
+        <v>101.743</v>
+      </c>
+      <c r="G152" s="6" t="n">
+        <v>-58.257</v>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J152" s="6" t="n">
+        <v>181.506</v>
+      </c>
+      <c r="K152" s="6" t="n">
+        <v>-18.494</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B153" s="4" t="n">
+        <v>146.632</v>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>-23.368</v>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>178.514</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>-96.486</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>156.229</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>-33.771</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B154" s="6" t="n">
+        <v>150.634</v>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>151.205</v>
+      </c>
+      <c r="G154" s="6" t="n">
+        <v>-38.795</v>
+      </c>
+      <c r="I154" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="J154" s="6" t="n">
+        <v>148.267</v>
+      </c>
+      <c r="K154" s="6" t="n">
+        <v>8.266999999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="B155" s="4" t="n">
+        <v>267.904</v>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>-22.096</v>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>151.912</v>
+      </c>
+      <c r="G155" s="4" t="n">
+        <v>81.91200000000001</v>
+      </c>
+      <c r="I155" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v>160.187</v>
+      </c>
+      <c r="K155" s="4" t="n">
+        <v>5.187</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>194.211</v>
+      </c>
+      <c r="C156" s="6" t="n">
+        <v>29.211</v>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F156" s="6" t="n">
+        <v>187.37</v>
+      </c>
+      <c r="G156" s="6" t="n">
+        <v>-7.63</v>
+      </c>
+      <c r="I156" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J156" s="6" t="n">
+        <v>164.524</v>
+      </c>
+      <c r="K156" s="6" t="n">
+        <v>-0.476</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B157" s="4" t="n">
+        <v>130.069</v>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>-9.930999999999999</v>
+      </c>
+      <c r="E157" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>94.604</v>
+      </c>
+      <c r="G157" s="4" t="n">
+        <v>19.604</v>
+      </c>
+      <c r="I157" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v>168.592</v>
+      </c>
+      <c r="K157" s="4" t="n">
+        <v>-1.408</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B158" s="6" t="n">
+        <v>80.874</v>
+      </c>
+      <c r="C158" s="6" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="G158" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I158" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="J158" s="6" t="n">
+        <v>174</v>
+      </c>
+      <c r="K158" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B159" s="4" t="n">
+        <v>117.997</v>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>-12.003</v>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>177.06</v>
+      </c>
+      <c r="G159" s="4" t="n">
+        <v>-47.94</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v>174.808</v>
+      </c>
+      <c r="K159" s="4" t="n">
+        <v>-10.192</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B160" s="6" t="n">
+        <v>129.808</v>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="I160" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="J160" s="6" t="n">
+        <v>190.063</v>
+      </c>
+      <c r="K160" s="6" t="n">
+        <v>-4.937</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B161" s="4" t="n">
+        <v>246.73</v>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="I161" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J161" s="4" t="n">
+        <v>196.484</v>
+      </c>
+      <c r="K161" s="4" t="n">
+        <v>-3.516</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B162" s="6" t="n">
+        <v>187.698</v>
+      </c>
+      <c r="C162" s="6" t="n">
+        <v>-12.302</v>
+      </c>
+      <c r="I162" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="J162" s="6" t="n">
+        <v>200.057</v>
+      </c>
+      <c r="K162" s="6" t="n">
+        <v>-4.943</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B163" s="4" t="n">
+        <v>54.584</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>4.584</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v>208.636</v>
+      </c>
+      <c r="K163" s="4" t="n">
+        <v>-6.364</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B164" s="6" t="n">
+        <v>76.872</v>
+      </c>
+      <c r="C164" s="6" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="I164" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J164" s="6" t="n">
+        <v>215.248</v>
+      </c>
+      <c r="K164" s="6" t="n">
+        <v>-4.752</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B165" s="4" t="n">
+        <v>146.769</v>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>-3.231</v>
+      </c>
+      <c r="I165" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J165" s="4" t="n">
+        <v>224.563</v>
+      </c>
+      <c r="K165" s="4" t="n">
+        <v>-25.437</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="B166" s="6" t="n">
+        <v>189.973</v>
+      </c>
+      <c r="C166" s="6" t="n">
+        <v>-15.027</v>
+      </c>
+      <c r="I166" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="J166" s="6" t="n">
+        <v>250.092</v>
+      </c>
+      <c r="K166" s="6" t="n">
+        <v>-4.908</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B167" s="4" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v>259.747</v>
+      </c>
+      <c r="K167" s="4" t="n">
+        <v>-5.253</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B168" s="6" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="I168" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="J168" s="6" t="n">
+        <v>264.187</v>
+      </c>
+      <c r="K168" s="6" t="n">
+        <v>-5.813</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B169" s="4" t="n">
+        <v>155.625</v>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>-4.375</v>
+      </c>
+      <c r="I169" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J169" s="4" t="n">
+        <v>264.402</v>
+      </c>
+      <c r="K169" s="4" t="n">
+        <v>-10.598</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="B170" s="6" t="n">
+        <v>167.648</v>
+      </c>
+      <c r="C170" s="6" t="n">
+        <v>-7.352</v>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="J170" s="6" t="n">
+        <v>95.654</v>
+      </c>
+      <c r="K170" s="6" t="n">
+        <v>-80.346</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="B171" s="4" t="n">
+        <v>250.496</v>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>-19.504</v>
+      </c>
+      <c r="I171" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="J171" s="4" t="n">
+        <v>113.811</v>
+      </c>
+      <c r="K171" s="4" t="n">
+        <v>-6.189</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="B172" s="6" t="n">
+        <v>237.944</v>
+      </c>
+      <c r="C172" s="6" t="n">
+        <v>-12.056</v>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J172" s="6" t="n">
+        <v>134.416</v>
+      </c>
+      <c r="K172" s="6" t="n">
+        <v>58.416</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B173" s="4" t="n">
+        <v>207.089</v>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>27.089</v>
+      </c>
+      <c r="I173" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="J173" s="4" t="n">
+        <v>123.281</v>
+      </c>
+      <c r="K173" s="4" t="n">
+        <v>-0.719</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B174" s="6" t="n">
+        <v>125.736</v>
+      </c>
+      <c r="C174" s="6" t="n">
+        <v>-4.264</v>
+      </c>
+      <c r="I174" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J174" s="6" t="n">
+        <v>134.672</v>
+      </c>
+      <c r="K174" s="6" t="n">
+        <v>4.672</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="B175" s="4" t="n">
+        <v>253.117</v>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>-21.883</v>
+      </c>
+      <c r="I175" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J175" s="4" t="n">
+        <v>137.334</v>
+      </c>
+      <c r="K175" s="4" t="n">
+        <v>-2.666</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="B176" s="6" t="n">
+        <v>241.341</v>
+      </c>
+      <c r="C176" s="6" t="n">
+        <v>-13.659</v>
+      </c>
+      <c r="I176" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="J176" s="6" t="n">
+        <v>140.12</v>
+      </c>
+      <c r="K176" s="6" t="n">
+        <v>-3.88</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4" t="n">
+        <v>167.376</v>
+      </c>
+      <c r="C177" s="4" t="n">
+        <v>-8.624000000000001</v>
+      </c>
+      <c r="I177" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>620.451</v>
+      </c>
+      <c r="K177" s="4" t="n">
+        <v>0.451</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B178" s="6" t="n">
+        <v>184.939</v>
+      </c>
+      <c r="C178" s="6" t="n">
+        <v>34.939</v>
+      </c>
+      <c r="I178" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J178" s="6" t="n">
+        <v>619.326</v>
+      </c>
+      <c r="K178" s="6" t="n">
+        <v>39.326</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B179" s="4" t="n">
+        <v>612.087</v>
+      </c>
+      <c r="C179" s="4" t="n">
+        <v>-7.913</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>592.388</v>
+      </c>
+      <c r="K179" s="4" t="n">
+        <v>42.388</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B180" s="6" t="n">
+        <v>38.058</v>
+      </c>
+      <c r="C180" s="6" t="n">
+        <v>-4.942</v>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="J180" s="6" t="n">
+        <v>624.831</v>
+      </c>
+      <c r="K180" s="6" t="n">
+        <v>-25.169</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B181" s="4" t="n">
+        <v>75.15300000000001</v>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="I181" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v>598.253</v>
+      </c>
+      <c r="K181" s="4" t="n">
+        <v>-21.747</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="B182" s="6" t="n">
+        <v>215.809</v>
+      </c>
+      <c r="C182" s="6" t="n">
+        <v>-4.191</v>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J182" s="6" t="n">
+        <v>600.1420000000001</v>
+      </c>
+      <c r="K182" s="6" t="n">
+        <v>20.142</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B183" s="4" t="n">
+        <v>195.806</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>-4.194</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>197.675</v>
+      </c>
+      <c r="K183" s="4" t="n">
+        <v>22.675</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B184" s="6" t="n">
+        <v>76.42400000000001</v>
+      </c>
+      <c r="C184" s="6" t="n">
+        <v>-9.576000000000001</v>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J184" s="6" t="n">
+        <v>197.163</v>
+      </c>
+      <c r="K184" s="6" t="n">
+        <v>-2.837</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B185" s="4" t="n">
+        <v>173.867</v>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>-26.133</v>
+      </c>
+      <c r="I185" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v>211.826</v>
+      </c>
+      <c r="K185" s="4" t="n">
+        <v>1.826</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B186" s="6" t="n">
+        <v>155.033</v>
+      </c>
+      <c r="C186" s="6" t="n">
+        <v>-9.967000000000001</v>
+      </c>
+      <c r="I186" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="J186" s="6" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="K186" s="6" t="n">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="4" t="n">
+        <v>166.63</v>
+      </c>
+      <c r="C187" s="4" t="n">
+        <v>-18.37</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>254.03</v>
+      </c>
+      <c r="K187" s="4" t="n">
+        <v>-30.97</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B188" s="6" t="n">
+        <v>118.815</v>
+      </c>
+      <c r="C188" s="6" t="n">
+        <v>-11.185</v>
+      </c>
+      <c r="I188" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="J188" s="6" t="n">
+        <v>191.034</v>
+      </c>
+      <c r="K188" s="6" t="n">
+        <v>-83.96599999999999</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B189" s="4" t="n">
+        <v>125.075</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>-18.925</v>
+      </c>
+      <c r="I189" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J189" s="4" t="n">
+        <v>255.607</v>
+      </c>
+      <c r="K189" s="4" t="n">
+        <v>-19.393</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="B190" s="6" t="n">
+        <v>152.888</v>
+      </c>
+      <c r="C190" s="6" t="n">
+        <v>-2.112</v>
+      </c>
+      <c r="I190" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J190" s="6" t="n">
+        <v>230.873</v>
+      </c>
+      <c r="K190" s="6" t="n">
+        <v>10.873</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="B191" s="4" t="n">
+        <v>206.743</v>
+      </c>
+      <c r="C191" s="4" t="n">
+        <v>-13.257</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J191" s="4" t="n">
+        <v>196.321</v>
+      </c>
+      <c r="K191" s="4" t="n">
+        <v>11.321</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B192" s="6" t="n">
+        <v>137.596</v>
+      </c>
+      <c r="C192" s="6" t="n">
+        <v>-7.404</v>
+      </c>
+      <c r="I192" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="J192" s="6" t="n">
+        <v>182.072</v>
+      </c>
+      <c r="K192" s="6" t="n">
+        <v>-27.928</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B193" s="4" t="n">
+        <v>160.801</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>-14.199</v>
+      </c>
+      <c r="I193" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>161.591</v>
+      </c>
+      <c r="K193" s="4" t="n">
+        <v>31.591</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="B194" s="6" t="n">
+        <v>578.158</v>
+      </c>
+      <c r="C194" s="6" t="n">
+        <v>-1.842</v>
+      </c>
+      <c r="I194" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J194" s="6" t="n">
+        <v>168.302</v>
+      </c>
+      <c r="K194" s="6" t="n">
+        <v>98.30200000000001</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B195" s="4" t="n">
+        <v>27.771</v>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>-4.229</v>
+      </c>
+      <c r="I195" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J195" s="4" t="n">
+        <v>144.85</v>
+      </c>
+      <c r="K195" s="4" t="n">
+        <v>-5.15</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B196" s="6" t="n">
+        <v>124.172</v>
+      </c>
+      <c r="C196" s="6" t="n">
+        <v>-15.828</v>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J196" s="6" t="n">
+        <v>153.942</v>
+      </c>
+      <c r="K196" s="6" t="n">
+        <v>-11.058</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B197" s="4" t="n">
+        <v>73.83799999999999</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>3.838</v>
+      </c>
+      <c r="I197" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v>214.875</v>
+      </c>
+      <c r="K197" s="4" t="n">
+        <v>-12.125</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B198" s="6" t="n">
+        <v>186.854</v>
+      </c>
+      <c r="C198" s="6" t="n">
+        <v>-23.146</v>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="J198" s="6" t="n">
+        <v>212.159</v>
+      </c>
+      <c r="K198" s="6" t="n">
+        <v>-10.841</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B199" s="4" t="n">
+        <v>222.79</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="I199" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v>171.924</v>
+      </c>
+      <c r="K199" s="4" t="n">
+        <v>-3.076</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B200" s="6" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="C200" s="6" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="J200" s="6" t="n">
+        <v>157.435</v>
+      </c>
+      <c r="K200" s="6" t="n">
+        <v>-15.565</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B201" s="4" t="n">
+        <v>103.254</v>
+      </c>
+      <c r="C201" s="4" t="n">
+        <v>-6.746</v>
+      </c>
+      <c r="I201" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J201" s="4" t="n">
+        <v>163.42</v>
+      </c>
+      <c r="K201" s="4" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B202" s="6" t="n">
+        <v>64.958</v>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>4.958</v>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J202" s="6" t="n">
+        <v>108.217</v>
+      </c>
+      <c r="K202" s="6" t="n">
+        <v>-36.783</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="B203" s="4" t="n">
+        <v>243.587</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>20.587</v>
+      </c>
+      <c r="I203" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J203" s="4" t="n">
+        <v>104.163</v>
+      </c>
+      <c r="K203" s="4" t="n">
+        <v>44.163</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B204" s="6" t="n">
+        <v>114.043</v>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>-9.957000000000001</v>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J204" s="6" t="n">
+        <v>80.601</v>
+      </c>
+      <c r="K204" s="6" t="n">
+        <v>30.601</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B205" s="4" t="n">
+        <v>181.721</v>
+      </c>
+      <c r="C205" s="4" t="n">
+        <v>-28.279</v>
+      </c>
+      <c r="I205" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J205" s="4" t="n">
+        <v>141.78</v>
+      </c>
+      <c r="K205" s="4" t="n">
+        <v>61.78</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B206" s="6" t="n">
+        <v>164.306</v>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>-8.694000000000001</v>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J206" s="6" t="n">
+        <v>74.623</v>
+      </c>
+      <c r="K206" s="6" t="n">
+        <v>-0.377</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B207" s="4" t="n">
+        <v>620.986</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="I207" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J207" s="4" t="n">
+        <v>84.363</v>
+      </c>
+      <c r="K207" s="4" t="n">
+        <v>24.363</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B208" s="6" t="n">
+        <v>197.141</v>
+      </c>
+      <c r="C208" s="6" t="n">
+        <v>-2.859</v>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="J208" s="6" t="n">
+        <v>193.321</v>
+      </c>
+      <c r="K208" s="6" t="n">
+        <v>-31.679</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="I209" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J209" s="4" t="n">
+        <v>166.459</v>
+      </c>
+      <c r="K209" s="4" t="n">
+        <v>-3.541</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="I210" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J210" s="6" t="n">
+        <v>90.328</v>
+      </c>
+      <c r="K210" s="6" t="n">
+        <v>50.328</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="I211" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="J211" s="4" t="n">
+        <v>57.924</v>
+      </c>
+      <c r="K211" s="4" t="n">
+        <v>-4.076</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="I212" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J212" s="6" t="n">
+        <v>115.416</v>
+      </c>
+      <c r="K212" s="6" t="n">
+        <v>40.416</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="I213" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="J213" s="4" t="n">
+        <v>142.575</v>
+      </c>
+      <c r="K213" s="4" t="n">
+        <v>32.575</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="I214" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="J214" s="6" t="n">
+        <v>107.784</v>
+      </c>
+      <c r="K214" s="6" t="n">
+        <v>-52.216</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="I215" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="J215" s="4" t="n">
+        <v>35.228</v>
+      </c>
+      <c r="K215" s="4" t="n">
+        <v>-50.772</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="I216" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="J216" s="6" t="n">
+        <v>62.699</v>
+      </c>
+      <c r="K216" s="6" t="n">
+        <v>19.699</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="I217" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="J217" s="4" t="n">
+        <v>45.451</v>
+      </c>
+      <c r="K217" s="4" t="n">
+        <v>13.451</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="I218" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J218" s="6" t="n">
+        <v>105.863</v>
+      </c>
+      <c r="K218" s="6" t="n">
+        <v>35.863</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="I219" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J219" s="4" t="n">
+        <v>136.898</v>
+      </c>
+      <c r="K219" s="4" t="n">
+        <v>76.898</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="I220" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J220" s="6" t="n">
+        <v>167.167</v>
+      </c>
+      <c r="K220" s="6" t="n">
+        <v>-32.833</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="I221" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J221" s="4" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="K221" s="4" t="n">
+        <v>66.95</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="I222" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J222" s="6" t="n">
+        <v>109.768</v>
+      </c>
+      <c r="K222" s="6" t="n">
+        <v>-40.232</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="I223" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J223" s="4" t="n">
+        <v>204.562</v>
+      </c>
+      <c r="K223" s="4" t="n">
+        <v>4.562</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="I224" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="J224" s="6" t="n">
+        <v>119.676</v>
+      </c>
+      <c r="K224" s="6" t="n">
+        <v>-35.324</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="I225" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J225" s="4" t="n">
+        <v>167.013</v>
+      </c>
+      <c r="K225" s="4" t="n">
+        <v>-22.987</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="I226" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J226" s="6" t="n">
+        <v>166.493</v>
+      </c>
+      <c r="K226" s="6" t="n">
+        <v>-53.507</v>
+      </c>
+    </row>
+    <row r="227"/>
+    <row r="228">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B229" s="12" t="n">
+        <v>11.4549</v>
+      </c>
+      <c r="C229" s="12" t="n">
+        <v>34.701</v>
+      </c>
+      <c r="D229" s="12" t="n">
+        <v>21.5545</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="n">
+        <v>199.9871</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>2126.9462</v>
+      </c>
+      <c r="D230" s="11" t="n">
+        <v>946.5408</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B231" s="12" t="n">
+        <v>14.1417</v>
+      </c>
+      <c r="C231" s="12" t="n">
+        <v>46.1188</v>
+      </c>
+      <c r="D231" s="12" t="n">
+        <v>30.7659</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B232" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C232" s="11" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="D232" s="11" t="n">
+        <v>0.9433</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>LMI</t>
+        </is>
+      </c>
+      <c r="B233" s="12" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="C233" s="12" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="D233" s="12" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>EAE</t>
+        </is>
+      </c>
+      <c r="B234" s="11" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="C234" s="11" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="D234" s="11" t="n">
+        <v>0.1994</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>VAF</t>
+        </is>
+      </c>
+      <c r="B235" s="12" t="n">
+        <v>99.0877</v>
+      </c>
+      <c r="C235" s="12" t="n">
+        <v>51.9025</v>
+      </c>
+      <c r="D235" s="12" t="n">
+        <v>94.33110000000001</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="B236" s="11" t="n">
+        <v>13.5353</v>
+      </c>
+      <c r="C236" s="11" t="n">
+        <v>43.7293</v>
+      </c>
+      <c r="D236" s="11" t="n">
+        <v>30.7648</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
+    <mergeCell ref="I141:K141"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A140:K140"/>
     <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="E141:G141"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="I73:K73"/>
@@ -23743,7 +25642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25949,10 +27848,1909 @@
         <v>30.5827</v>
       </c>
     </row>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B148" s="4" t="n">
+        <v>53.427</v>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>-8.573</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>210.322</v>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>-9.678000000000001</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>195.488</v>
+      </c>
+      <c r="K148" s="4" t="n">
+        <v>5.488</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>547.998</v>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>-2.002</v>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>158.695</v>
+      </c>
+      <c r="G149" s="6" t="n">
+        <v>-11.305</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>180.126</v>
+      </c>
+      <c r="K149" s="6" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>580</v>
+      </c>
+      <c r="B150" s="4" t="n">
+        <v>580.299</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>152.236</v>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>-2.764</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J150" s="4" t="n">
+        <v>157.285</v>
+      </c>
+      <c r="K150" s="4" t="n">
+        <v>-2.715</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>173.989</v>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>-6.011</v>
+      </c>
+      <c r="E151" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>235.704</v>
+      </c>
+      <c r="G151" s="6" t="n">
+        <v>-49.296</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>134.867</v>
+      </c>
+      <c r="K151" s="6" t="n">
+        <v>4.867</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>178.129</v>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>-6.871</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>152.158</v>
+      </c>
+      <c r="G152" s="4" t="n">
+        <v>-7.842</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <v>188.338</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>-21.662</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>269.619</v>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>-5.381</v>
+      </c>
+      <c r="E153" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>124.126</v>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v>64.126</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>191.428</v>
+      </c>
+      <c r="K153" s="6" t="n">
+        <v>11.428</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B154" s="4" t="n">
+        <v>182.873</v>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>-7.127</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>195.275</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>20.275</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>170.512</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>10.512</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="B155" s="6" t="n">
+        <v>259.158</v>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>-5.842</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>212.785</v>
+      </c>
+      <c r="G155" s="6" t="n">
+        <v>-2.215</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>134.768</v>
+      </c>
+      <c r="K155" s="6" t="n">
+        <v>4.768</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>646.498</v>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>-3.502</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>110.153</v>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>-9.847</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>209.541</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <v>-0.459</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>32.928</v>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>-7.072</v>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>107.903</v>
+      </c>
+      <c r="G157" s="6" t="n">
+        <v>-52.097</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>197.004</v>
+      </c>
+      <c r="K157" s="6" t="n">
+        <v>-2.996</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B158" s="4" t="n">
+        <v>162.769</v>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>-7.231</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>209.841</v>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>-65.15900000000001</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>170.999</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>-19.001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>143.322</v>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>-6.678</v>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>155.376</v>
+      </c>
+      <c r="G159" s="6" t="n">
+        <v>-34.624</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>153.583</v>
+      </c>
+      <c r="K159" s="6" t="n">
+        <v>13.583</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="B160" s="4" t="n">
+        <v>284.148</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>-5.852</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>137.327</v>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>67.327</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>163.194</v>
+      </c>
+      <c r="K160" s="4" t="n">
+        <v>8.194000000000001</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B161" s="6" t="n">
+        <v>156.183</v>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>-8.817</v>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>181.565</v>
+      </c>
+      <c r="G161" s="6" t="n">
+        <v>-13.435</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>167.919</v>
+      </c>
+      <c r="K161" s="6" t="n">
+        <v>2.919</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B162" s="4" t="n">
+        <v>132.689</v>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>-7.311</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>100.275</v>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>25.275</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>169.413</v>
+      </c>
+      <c r="K162" s="4" t="n">
+        <v>-0.587</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B163" s="6" t="n">
+        <v>73.515</v>
+      </c>
+      <c r="C163" s="6" t="n">
+        <v>-6.485</v>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>178.472</v>
+      </c>
+      <c r="G163" s="6" t="n">
+        <v>-21.528</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>176.603</v>
+      </c>
+      <c r="K163" s="6" t="n">
+        <v>1.603</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B164" s="4" t="n">
+        <v>122.854</v>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>-7.146</v>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>212.627</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>-12.373</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J164" s="4" t="n">
+        <v>181.394</v>
+      </c>
+      <c r="K164" s="4" t="n">
+        <v>-3.606</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="C165" s="6" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="J165" s="6" t="n">
+        <v>188.721</v>
+      </c>
+      <c r="K165" s="6" t="n">
+        <v>-6.279</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B166" s="4" t="n">
+        <v>218.267</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>-8.733000000000001</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>196.475</v>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>-3.525</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>193.706</v>
+      </c>
+      <c r="C167" s="6" t="n">
+        <v>-6.294</v>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="J167" s="6" t="n">
+        <v>207.54</v>
+      </c>
+      <c r="K167" s="6" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B168" s="4" t="n">
+        <v>44.801</v>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>-5.199</v>
+      </c>
+      <c r="I168" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>215.635</v>
+      </c>
+      <c r="K168" s="4" t="n">
+        <v>0.635</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B169" s="6" t="n">
+        <v>69.997</v>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>-6.003</v>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>229.926</v>
+      </c>
+      <c r="K169" s="6" t="n">
+        <v>9.926</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B170" s="4" t="n">
+        <v>143.295</v>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>-6.705</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J170" s="4" t="n">
+        <v>216.943</v>
+      </c>
+      <c r="K170" s="4" t="n">
+        <v>-33.057</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="B171" s="6" t="n">
+        <v>198.261</v>
+      </c>
+      <c r="C171" s="6" t="n">
+        <v>-6.739</v>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>254.726</v>
+      </c>
+      <c r="K171" s="6" t="n">
+        <v>-0.274</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B172" s="4" t="n">
+        <v>46.061</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>-3.939</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="K172" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B173" s="6" t="n">
+        <v>201.723</v>
+      </c>
+      <c r="C173" s="6" t="n">
+        <v>-8.276999999999999</v>
+      </c>
+      <c r="I173" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="J173" s="6" t="n">
+        <v>269.755</v>
+      </c>
+      <c r="K173" s="6" t="n">
+        <v>-0.245</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B174" s="4" t="n">
+        <v>152.621</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>-7.379</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>279.336</v>
+      </c>
+      <c r="K174" s="4" t="n">
+        <v>4.336</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="B175" s="6" t="n">
+        <v>169.34</v>
+      </c>
+      <c r="C175" s="6" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="I175" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="J175" s="6" t="n">
+        <v>106.587</v>
+      </c>
+      <c r="K175" s="6" t="n">
+        <v>-69.413</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="B176" s="4" t="n">
+        <v>263.285</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>-6.715</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>115.412</v>
+      </c>
+      <c r="K176" s="4" t="n">
+        <v>-4.588</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="B177" s="6" t="n">
+        <v>243.95</v>
+      </c>
+      <c r="C177" s="6" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J177" s="6" t="n">
+        <v>129.507</v>
+      </c>
+      <c r="K177" s="6" t="n">
+        <v>53.507</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B178" s="4" t="n">
+        <v>172.624</v>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>-7.376</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>120.457</v>
+      </c>
+      <c r="K178" s="4" t="n">
+        <v>-3.543</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B179" s="6" t="n">
+        <v>123.305</v>
+      </c>
+      <c r="C179" s="6" t="n">
+        <v>-6.695</v>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>131.733</v>
+      </c>
+      <c r="K179" s="6" t="n">
+        <v>1.733</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="B180" s="4" t="n">
+        <v>268.61</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>133.821</v>
+      </c>
+      <c r="K180" s="4" t="n">
+        <v>-6.179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="B181" s="6" t="n">
+        <v>249.425</v>
+      </c>
+      <c r="C181" s="6" t="n">
+        <v>-5.575</v>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>136.489</v>
+      </c>
+      <c r="K181" s="6" t="n">
+        <v>-7.511</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B182" s="4" t="n">
+        <v>169.321</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>-6.679</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>629.176</v>
+      </c>
+      <c r="K182" s="4" t="n">
+        <v>9.176</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>142.813</v>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>-7.187</v>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J183" s="6" t="n">
+        <v>615.357</v>
+      </c>
+      <c r="K183" s="6" t="n">
+        <v>35.357</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B184" s="4" t="n">
+        <v>616.324</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>-3.676</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>581.878</v>
+      </c>
+      <c r="K184" s="4" t="n">
+        <v>31.878</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B185" s="6" t="n">
+        <v>42.918</v>
+      </c>
+      <c r="C185" s="6" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>635.196</v>
+      </c>
+      <c r="K185" s="6" t="n">
+        <v>-14.804</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B186" s="4" t="n">
+        <v>62.988</v>
+      </c>
+      <c r="C186" s="4" t="n">
+        <v>-12.012</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>612.833</v>
+      </c>
+      <c r="K186" s="4" t="n">
+        <v>-7.167</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="B187" s="6" t="n">
+        <v>212.305</v>
+      </c>
+      <c r="C187" s="6" t="n">
+        <v>-7.695</v>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J187" s="6" t="n">
+        <v>614.115</v>
+      </c>
+      <c r="K187" s="6" t="n">
+        <v>34.115</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B188" s="4" t="n">
+        <v>193.182</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>-6.818</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J188" s="4" t="n">
+        <v>200.666</v>
+      </c>
+      <c r="K188" s="4" t="n">
+        <v>25.666</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B189" s="6" t="n">
+        <v>42.918</v>
+      </c>
+      <c r="C189" s="6" t="n">
+        <v>-43.082</v>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J189" s="6" t="n">
+        <v>196.025</v>
+      </c>
+      <c r="K189" s="6" t="n">
+        <v>-3.975</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B190" s="4" t="n">
+        <v>193.516</v>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>-6.484</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>216.361</v>
+      </c>
+      <c r="K190" s="4" t="n">
+        <v>6.361</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B191" s="6" t="n">
+        <v>158.332</v>
+      </c>
+      <c r="C191" s="6" t="n">
+        <v>-6.668</v>
+      </c>
+      <c r="I191" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>283.252</v>
+      </c>
+      <c r="K191" s="6" t="n">
+        <v>-6.748</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B192" s="4" t="n">
+        <v>178.167</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>-6.833</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>253.968</v>
+      </c>
+      <c r="K192" s="4" t="n">
+        <v>-31.032</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B193" s="6" t="n">
+        <v>123.572</v>
+      </c>
+      <c r="C193" s="6" t="n">
+        <v>-6.428</v>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>165.248</v>
+      </c>
+      <c r="K193" s="6" t="n">
+        <v>-109.752</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B194" s="4" t="n">
+        <v>136.231</v>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>-7.769</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>259.522</v>
+      </c>
+      <c r="K194" s="4" t="n">
+        <v>-15.478</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="B195" s="6" t="n">
+        <v>146.801</v>
+      </c>
+      <c r="C195" s="6" t="n">
+        <v>-8.199</v>
+      </c>
+      <c r="I195" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>229.718</v>
+      </c>
+      <c r="K195" s="6" t="n">
+        <v>9.718</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="B196" s="4" t="n">
+        <v>213.378</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>-6.622</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J196" s="4" t="n">
+        <v>235.47</v>
+      </c>
+      <c r="K196" s="4" t="n">
+        <v>50.47</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B197" s="6" t="n">
+        <v>135.273</v>
+      </c>
+      <c r="C197" s="6" t="n">
+        <v>-9.727</v>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="J197" s="6" t="n">
+        <v>184.307</v>
+      </c>
+      <c r="K197" s="6" t="n">
+        <v>-25.693</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B198" s="4" t="n">
+        <v>168.306</v>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>-6.694</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>166.025</v>
+      </c>
+      <c r="K198" s="4" t="n">
+        <v>36.025</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="B199" s="6" t="n">
+        <v>578.213</v>
+      </c>
+      <c r="C199" s="6" t="n">
+        <v>-1.787</v>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>162.402</v>
+      </c>
+      <c r="K199" s="6" t="n">
+        <v>92.402</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B200" s="4" t="n">
+        <v>42.918</v>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>10.918</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J200" s="4" t="n">
+        <v>117.712</v>
+      </c>
+      <c r="K200" s="4" t="n">
+        <v>-32.288</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B201" s="6" t="n">
+        <v>132.581</v>
+      </c>
+      <c r="C201" s="6" t="n">
+        <v>-7.419</v>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>147.34</v>
+      </c>
+      <c r="K201" s="6" t="n">
+        <v>-17.66</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B202" s="4" t="n">
+        <v>63.444</v>
+      </c>
+      <c r="C202" s="4" t="n">
+        <v>-6.556</v>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="J202" s="4" t="n">
+        <v>220.296</v>
+      </c>
+      <c r="K202" s="4" t="n">
+        <v>-6.704</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B203" s="6" t="n">
+        <v>202.829</v>
+      </c>
+      <c r="C203" s="6" t="n">
+        <v>-7.171</v>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>218.022</v>
+      </c>
+      <c r="K203" s="6" t="n">
+        <v>-4.978</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B204" s="4" t="n">
+        <v>203.953</v>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>-6.047</v>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J204" s="4" t="n">
+        <v>170.132</v>
+      </c>
+      <c r="K204" s="4" t="n">
+        <v>-4.868</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>55.136</v>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>-4.864</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>165.066</v>
+      </c>
+      <c r="K205" s="6" t="n">
+        <v>-7.934</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B206" s="4" t="n">
+        <v>102.095</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>-7.905</v>
+      </c>
+      <c r="I206" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J206" s="4" t="n">
+        <v>163.363</v>
+      </c>
+      <c r="K206" s="4" t="n">
+        <v>13.363</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B207" s="6" t="n">
+        <v>55.762</v>
+      </c>
+      <c r="C207" s="6" t="n">
+        <v>-4.238</v>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>102.004</v>
+      </c>
+      <c r="K207" s="6" t="n">
+        <v>-42.996</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="B208" s="4" t="n">
+        <v>215.514</v>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>-7.486</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J208" s="4" t="n">
+        <v>93.672</v>
+      </c>
+      <c r="K208" s="4" t="n">
+        <v>33.672</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B209" s="6" t="n">
+        <v>116.782</v>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>-7.218</v>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J209" s="6" t="n">
+        <v>78.06100000000001</v>
+      </c>
+      <c r="K209" s="6" t="n">
+        <v>28.061</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B210" s="4" t="n">
+        <v>203.082</v>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>-6.918</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J210" s="4" t="n">
+        <v>135.168</v>
+      </c>
+      <c r="K210" s="4" t="n">
+        <v>55.168</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B211" s="6" t="n">
+        <v>162.769</v>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>-10.231</v>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J211" s="6" t="n">
+        <v>55.204</v>
+      </c>
+      <c r="K211" s="6" t="n">
+        <v>-19.796</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B212" s="4" t="n">
+        <v>618.822</v>
+      </c>
+      <c r="C212" s="4" t="n">
+        <v>-1.178</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J212" s="4" t="n">
+        <v>67.702</v>
+      </c>
+      <c r="K212" s="4" t="n">
+        <v>7.702</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B213" s="6" t="n">
+        <v>192.321</v>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>-7.679</v>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="J213" s="6" t="n">
+        <v>201.204</v>
+      </c>
+      <c r="K213" s="6" t="n">
+        <v>-23.796</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="I214" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J214" s="4" t="n">
+        <v>166.703</v>
+      </c>
+      <c r="K214" s="4" t="n">
+        <v>-3.297</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="I215" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J215" s="6" t="n">
+        <v>79.155</v>
+      </c>
+      <c r="K215" s="6" t="n">
+        <v>39.155</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="I216" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="J216" s="4" t="n">
+        <v>57.092</v>
+      </c>
+      <c r="K216" s="4" t="n">
+        <v>-4.908</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="I217" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J217" s="6" t="n">
+        <v>113.426</v>
+      </c>
+      <c r="K217" s="6" t="n">
+        <v>38.426</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="I218" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="J218" s="4" t="n">
+        <v>152.025</v>
+      </c>
+      <c r="K218" s="4" t="n">
+        <v>42.025</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="I219" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="J219" s="6" t="n">
+        <v>105.345</v>
+      </c>
+      <c r="K219" s="6" t="n">
+        <v>-54.655</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="I220" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="J220" s="4" t="n">
+        <v>34.477</v>
+      </c>
+      <c r="K220" s="4" t="n">
+        <v>-51.523</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="I221" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="J221" s="6" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="K221" s="6" t="n">
+        <v>17.38</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="I222" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="J222" s="4" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="K222" s="4" t="n">
+        <v>32.45</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="I223" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J223" s="6" t="n">
+        <v>77.94499999999999</v>
+      </c>
+      <c r="K223" s="6" t="n">
+        <v>7.945</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="I224" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J224" s="4" t="n">
+        <v>136.712</v>
+      </c>
+      <c r="K224" s="4" t="n">
+        <v>76.712</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="I225" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J225" s="6" t="n">
+        <v>166.477</v>
+      </c>
+      <c r="K225" s="6" t="n">
+        <v>-33.523</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="I226" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J226" s="4" t="n">
+        <v>119.465</v>
+      </c>
+      <c r="K226" s="4" t="n">
+        <v>69.465</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="I227" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J227" s="6" t="n">
+        <v>100.453</v>
+      </c>
+      <c r="K227" s="6" t="n">
+        <v>-49.547</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="I228" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J228" s="4" t="n">
+        <v>206.095</v>
+      </c>
+      <c r="K228" s="4" t="n">
+        <v>6.095</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="I229" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="J229" s="6" t="n">
+        <v>118.737</v>
+      </c>
+      <c r="K229" s="6" t="n">
+        <v>-36.263</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="I230" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>191.163</v>
+      </c>
+      <c r="K230" s="4" t="n">
+        <v>1.163</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="I231" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J231" s="6" t="n">
+        <v>148.062</v>
+      </c>
+      <c r="K231" s="6" t="n">
+        <v>-71.938</v>
+      </c>
+    </row>
+    <row r="232"/>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="n">
+        <v>7.0191</v>
+      </c>
+      <c r="C234" s="12" t="n">
+        <v>27.598</v>
+      </c>
+      <c r="D234" s="12" t="n">
+        <v>21.4866</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="n">
+        <v>73.7843</v>
+      </c>
+      <c r="C235" s="11" t="n">
+        <v>1263.1275</v>
+      </c>
+      <c r="D235" s="11" t="n">
+        <v>996.004</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="n">
+        <v>8.5898</v>
+      </c>
+      <c r="C236" s="12" t="n">
+        <v>35.5405</v>
+      </c>
+      <c r="D236" s="12" t="n">
+        <v>31.5595</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B237" s="11" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="C237" s="11" t="n">
+        <v>0.6823</v>
+      </c>
+      <c r="D237" s="11" t="n">
+        <v>0.9403</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>LMI</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="C238" s="12" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="D238" s="12" t="n">
+        <v>0.7352</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>EAE</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>0.2296</v>
+      </c>
+      <c r="D239" s="11" t="n">
+        <v>0.1977</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>VAF</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="n">
+        <v>99.85469999999999</v>
+      </c>
+      <c r="C240" s="12" t="n">
+        <v>69.3836</v>
+      </c>
+      <c r="D240" s="12" t="n">
+        <v>94.03830000000001</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="B241" s="11" t="n">
+        <v>5.4012</v>
+      </c>
+      <c r="C241" s="11" t="n">
+        <v>34.889</v>
+      </c>
+      <c r="D241" s="11" t="n">
+        <v>31.5493</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
+    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A72:K72"/>
+    <mergeCell ref="E146:G146"/>
+    <mergeCell ref="I146:K146"/>
+    <mergeCell ref="A146:C146"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="I73:K73"/>
@@ -25971,7 +29769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28177,10 +31975,1909 @@
         <v>33.27</v>
       </c>
     </row>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B148" s="4" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>218.77</v>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>200.193</v>
+      </c>
+      <c r="K148" s="4" t="n">
+        <v>10.193</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>548.6369999999999</v>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>-1.363</v>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>174.565</v>
+      </c>
+      <c r="G149" s="6" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="I149" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J149" s="6" t="n">
+        <v>179.934</v>
+      </c>
+      <c r="K149" s="6" t="n">
+        <v>-0.066</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>580</v>
+      </c>
+      <c r="B150" s="4" t="n">
+        <v>581.6319999999999</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>154.471</v>
+      </c>
+      <c r="G150" s="4" t="n">
+        <v>-0.529</v>
+      </c>
+      <c r="I150" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J150" s="4" t="n">
+        <v>153.271</v>
+      </c>
+      <c r="K150" s="4" t="n">
+        <v>-6.729</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>181.924</v>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="E151" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>233.464</v>
+      </c>
+      <c r="G151" s="6" t="n">
+        <v>-51.536</v>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J151" s="6" t="n">
+        <v>128.185</v>
+      </c>
+      <c r="K151" s="6" t="n">
+        <v>-1.815</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>185.602</v>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>163.528</v>
+      </c>
+      <c r="G152" s="4" t="n">
+        <v>3.528</v>
+      </c>
+      <c r="I152" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <v>187.228</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <v>-22.772</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>276.055</v>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="E153" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>116.679</v>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v>56.679</v>
+      </c>
+      <c r="I153" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="J153" s="6" t="n">
+        <v>189.909</v>
+      </c>
+      <c r="K153" s="6" t="n">
+        <v>9.909000000000001</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B154" s="4" t="n">
+        <v>191.041</v>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>189.789</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>14.789</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>173.182</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <v>13.182</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="B155" s="6" t="n">
+        <v>265.235</v>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>214.074</v>
+      </c>
+      <c r="G155" s="6" t="n">
+        <v>-0.926</v>
+      </c>
+      <c r="I155" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J155" s="6" t="n">
+        <v>130.625</v>
+      </c>
+      <c r="K155" s="6" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>649.9640000000001</v>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>121.743</v>
+      </c>
+      <c r="G156" s="4" t="n">
+        <v>1.743</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <v>217.718</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <v>7.718</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>40.126</v>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>110.218</v>
+      </c>
+      <c r="G157" s="6" t="n">
+        <v>-49.782</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J157" s="6" t="n">
+        <v>195.786</v>
+      </c>
+      <c r="K157" s="6" t="n">
+        <v>-4.214</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B158" s="4" t="n">
+        <v>170.223</v>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>204.69</v>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>-70.31</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>175.956</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <v>-14.044</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>150.322</v>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="E159" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>170.486</v>
+      </c>
+      <c r="G159" s="6" t="n">
+        <v>-19.514</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="J159" s="6" t="n">
+        <v>159.299</v>
+      </c>
+      <c r="K159" s="6" t="n">
+        <v>19.299</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="B160" s="4" t="n">
+        <v>290.134</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>134.805</v>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>64.80500000000001</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>158.073</v>
+      </c>
+      <c r="K160" s="4" t="n">
+        <v>3.073</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B161" s="6" t="n">
+        <v>164.979</v>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="E161" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>192.336</v>
+      </c>
+      <c r="G161" s="6" t="n">
+        <v>-2.664</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J161" s="6" t="n">
+        <v>172.344</v>
+      </c>
+      <c r="K161" s="6" t="n">
+        <v>7.344</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B162" s="4" t="n">
+        <v>139.749</v>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>-0.251</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>101.011</v>
+      </c>
+      <c r="G162" s="4" t="n">
+        <v>26.011</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J162" s="4" t="n">
+        <v>175.208</v>
+      </c>
+      <c r="K162" s="4" t="n">
+        <v>5.208</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B163" s="6" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="C163" s="6" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="E163" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>188.831</v>
+      </c>
+      <c r="G163" s="6" t="n">
+        <v>-11.169</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="J163" s="6" t="n">
+        <v>178.887</v>
+      </c>
+      <c r="K163" s="6" t="n">
+        <v>3.887</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B164" s="4" t="n">
+        <v>130.766</v>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>220.797</v>
+      </c>
+      <c r="G164" s="4" t="n">
+        <v>-4.203</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J164" s="4" t="n">
+        <v>176.759</v>
+      </c>
+      <c r="K164" s="4" t="n">
+        <v>-8.241</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>129.719</v>
+      </c>
+      <c r="C165" s="6" t="n">
+        <v>-0.281</v>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="J165" s="6" t="n">
+        <v>187.161</v>
+      </c>
+      <c r="K165" s="6" t="n">
+        <v>-7.839</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="B166" s="4" t="n">
+        <v>225.918</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>-1.082</v>
+      </c>
+      <c r="I166" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J166" s="4" t="n">
+        <v>194.491</v>
+      </c>
+      <c r="K166" s="4" t="n">
+        <v>-5.509</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>199.755</v>
+      </c>
+      <c r="C167" s="6" t="n">
+        <v>-0.245</v>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="J167" s="6" t="n">
+        <v>197.025</v>
+      </c>
+      <c r="K167" s="6" t="n">
+        <v>-7.975</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B168" s="4" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I168" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="J168" s="4" t="n">
+        <v>221.729</v>
+      </c>
+      <c r="K168" s="4" t="n">
+        <v>6.729</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B169" s="6" t="n">
+        <v>76.444</v>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J169" s="6" t="n">
+        <v>228.251</v>
+      </c>
+      <c r="K169" s="6" t="n">
+        <v>8.250999999999999</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B170" s="4" t="n">
+        <v>151.284</v>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J170" s="4" t="n">
+        <v>217.611</v>
+      </c>
+      <c r="K170" s="4" t="n">
+        <v>-32.389</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="B171" s="6" t="n">
+        <v>204.417</v>
+      </c>
+      <c r="C171" s="6" t="n">
+        <v>-0.583</v>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="J171" s="6" t="n">
+        <v>249.648</v>
+      </c>
+      <c r="K171" s="6" t="n">
+        <v>-5.352</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B172" s="4" t="n">
+        <v>50.786</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="J172" s="4" t="n">
+        <v>264.23</v>
+      </c>
+      <c r="K172" s="4" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B173" s="6" t="n">
+        <v>206.861</v>
+      </c>
+      <c r="C173" s="6" t="n">
+        <v>-3.139</v>
+      </c>
+      <c r="I173" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="J173" s="6" t="n">
+        <v>268.206</v>
+      </c>
+      <c r="K173" s="6" t="n">
+        <v>-1.794</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B174" s="4" t="n">
+        <v>159.208</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>-0.792</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J174" s="4" t="n">
+        <v>275.586</v>
+      </c>
+      <c r="K174" s="4" t="n">
+        <v>0.586</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="B175" s="6" t="n">
+        <v>176.068</v>
+      </c>
+      <c r="C175" s="6" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="I175" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="J175" s="6" t="n">
+        <v>108.763</v>
+      </c>
+      <c r="K175" s="6" t="n">
+        <v>-67.23699999999999</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="B176" s="4" t="n">
+        <v>269.701</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>-0.299</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>118.497</v>
+      </c>
+      <c r="K176" s="4" t="n">
+        <v>-1.503</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="B177" s="6" t="n">
+        <v>249.152</v>
+      </c>
+      <c r="C177" s="6" t="n">
+        <v>-0.848</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J177" s="6" t="n">
+        <v>118.282</v>
+      </c>
+      <c r="K177" s="6" t="n">
+        <v>42.282</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B178" s="4" t="n">
+        <v>179.899</v>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>-0.101</v>
+      </c>
+      <c r="I178" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>123.003</v>
+      </c>
+      <c r="K178" s="4" t="n">
+        <v>-0.997</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B179" s="6" t="n">
+        <v>130.926</v>
+      </c>
+      <c r="C179" s="6" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="J179" s="6" t="n">
+        <v>134.043</v>
+      </c>
+      <c r="K179" s="6" t="n">
+        <v>4.043</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="B180" s="4" t="n">
+        <v>274.657</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>-0.343</v>
+      </c>
+      <c r="I180" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J180" s="4" t="n">
+        <v>131.342</v>
+      </c>
+      <c r="K180" s="4" t="n">
+        <v>-8.657999999999999</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="B181" s="6" t="n">
+        <v>255.273</v>
+      </c>
+      <c r="C181" s="6" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I181" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="J181" s="6" t="n">
+        <v>133.286</v>
+      </c>
+      <c r="K181" s="6" t="n">
+        <v>-10.714</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B182" s="4" t="n">
+        <v>175.257</v>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>-0.743</v>
+      </c>
+      <c r="I182" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J182" s="4" t="n">
+        <v>623.785</v>
+      </c>
+      <c r="K182" s="4" t="n">
+        <v>3.785</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>149.855</v>
+      </c>
+      <c r="C183" s="6" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J183" s="6" t="n">
+        <v>587.717</v>
+      </c>
+      <c r="K183" s="6" t="n">
+        <v>7.717</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B184" s="4" t="n">
+        <v>618.284</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>-1.716</v>
+      </c>
+      <c r="I184" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="J184" s="4" t="n">
+        <v>558.311</v>
+      </c>
+      <c r="K184" s="4" t="n">
+        <v>8.311</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B185" s="6" t="n">
+        <v>52.439</v>
+      </c>
+      <c r="C185" s="6" t="n">
+        <v>9.439</v>
+      </c>
+      <c r="I185" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="J185" s="6" t="n">
+        <v>644.414</v>
+      </c>
+      <c r="K185" s="6" t="n">
+        <v>-5.586</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B186" s="4" t="n">
+        <v>70.11499999999999</v>
+      </c>
+      <c r="C186" s="4" t="n">
+        <v>-4.885</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>601.063</v>
+      </c>
+      <c r="K186" s="4" t="n">
+        <v>-18.937</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="B187" s="6" t="n">
+        <v>219.909</v>
+      </c>
+      <c r="C187" s="6" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="I187" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="J187" s="6" t="n">
+        <v>590.146</v>
+      </c>
+      <c r="K187" s="6" t="n">
+        <v>10.146</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B188" s="4" t="n">
+        <v>200.669</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J188" s="4" t="n">
+        <v>190.771</v>
+      </c>
+      <c r="K188" s="4" t="n">
+        <v>15.771</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B189" s="6" t="n">
+        <v>52.439</v>
+      </c>
+      <c r="C189" s="6" t="n">
+        <v>-33.561</v>
+      </c>
+      <c r="I189" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J189" s="6" t="n">
+        <v>193.441</v>
+      </c>
+      <c r="K189" s="6" t="n">
+        <v>-6.559</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B190" s="4" t="n">
+        <v>199.538</v>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>-0.462</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>216.986</v>
+      </c>
+      <c r="K190" s="4" t="n">
+        <v>6.986</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B191" s="6" t="n">
+        <v>165.096</v>
+      </c>
+      <c r="C191" s="6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="I191" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>293.39</v>
+      </c>
+      <c r="K191" s="6" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B192" s="4" t="n">
+        <v>183.715</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>246.922</v>
+      </c>
+      <c r="K192" s="4" t="n">
+        <v>-38.078</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B193" s="6" t="n">
+        <v>130.854</v>
+      </c>
+      <c r="C193" s="6" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="I193" s="6" t="n">
+        <v>275</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>198.008</v>
+      </c>
+      <c r="K193" s="6" t="n">
+        <v>-76.992</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B194" s="4" t="n">
+        <v>143.395</v>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>-0.605</v>
+      </c>
+      <c r="I194" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>247.131</v>
+      </c>
+      <c r="K194" s="4" t="n">
+        <v>-27.869</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="B195" s="6" t="n">
+        <v>154.21</v>
+      </c>
+      <c r="C195" s="6" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="I195" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>224.947</v>
+      </c>
+      <c r="K195" s="6" t="n">
+        <v>4.947</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="B196" s="4" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="J196" s="4" t="n">
+        <v>215.851</v>
+      </c>
+      <c r="K196" s="4" t="n">
+        <v>30.851</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B197" s="6" t="n">
+        <v>142.11</v>
+      </c>
+      <c r="C197" s="6" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="J197" s="6" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="K197" s="6" t="n">
+        <v>-25.95</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B198" s="4" t="n">
+        <v>175.655</v>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>158.796</v>
+      </c>
+      <c r="K198" s="4" t="n">
+        <v>28.796</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="n">
+        <v>580</v>
+      </c>
+      <c r="B199" s="6" t="n">
+        <v>581.4829999999999</v>
+      </c>
+      <c r="C199" s="6" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J199" s="6" t="n">
+        <v>149.161</v>
+      </c>
+      <c r="K199" s="6" t="n">
+        <v>79.161</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B200" s="4" t="n">
+        <v>52.439</v>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>20.439</v>
+      </c>
+      <c r="I200" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J200" s="4" t="n">
+        <v>104.524</v>
+      </c>
+      <c r="K200" s="4" t="n">
+        <v>-45.476</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B201" s="6" t="n">
+        <v>139.165</v>
+      </c>
+      <c r="C201" s="6" t="n">
+        <v>-0.835</v>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J201" s="6" t="n">
+        <v>157.548</v>
+      </c>
+      <c r="K201" s="6" t="n">
+        <v>-7.452</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B202" s="4" t="n">
+        <v>69.858</v>
+      </c>
+      <c r="C202" s="4" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="I202" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="J202" s="4" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="K202" s="4" t="n">
+        <v>-6.69</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="B203" s="6" t="n">
+        <v>209.515</v>
+      </c>
+      <c r="C203" s="6" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="J203" s="6" t="n">
+        <v>225.084</v>
+      </c>
+      <c r="K203" s="6" t="n">
+        <v>2.084</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B204" s="4" t="n">
+        <v>211.257</v>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="I204" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J204" s="4" t="n">
+        <v>175.553</v>
+      </c>
+      <c r="K204" s="4" t="n">
+        <v>0.553</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>62.526</v>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>2.526</v>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="J205" s="6" t="n">
+        <v>166.087</v>
+      </c>
+      <c r="K205" s="6" t="n">
+        <v>-6.913</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B206" s="4" t="n">
+        <v>109.704</v>
+      </c>
+      <c r="C206" s="4" t="n">
+        <v>-0.296</v>
+      </c>
+      <c r="I206" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J206" s="4" t="n">
+        <v>162.68</v>
+      </c>
+      <c r="K206" s="4" t="n">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B207" s="6" t="n">
+        <v>63.215</v>
+      </c>
+      <c r="C207" s="6" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="J207" s="6" t="n">
+        <v>114.308</v>
+      </c>
+      <c r="K207" s="6" t="n">
+        <v>-30.692</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="B208" s="4" t="n">
+        <v>223.445</v>
+      </c>
+      <c r="C208" s="4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="I208" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J208" s="4" t="n">
+        <v>93.40300000000001</v>
+      </c>
+      <c r="K208" s="4" t="n">
+        <v>33.403</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B209" s="6" t="n">
+        <v>124.003</v>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J209" s="6" t="n">
+        <v>65.01300000000001</v>
+      </c>
+      <c r="K209" s="6" t="n">
+        <v>15.013</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B210" s="4" t="n">
+        <v>210.719</v>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="I210" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J210" s="4" t="n">
+        <v>139.897</v>
+      </c>
+      <c r="K210" s="4" t="n">
+        <v>59.897</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B211" s="6" t="n">
+        <v>170.223</v>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>-2.777</v>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J211" s="6" t="n">
+        <v>50.456</v>
+      </c>
+      <c r="K211" s="6" t="n">
+        <v>-24.544</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="B212" s="4" t="n">
+        <v>620.385</v>
+      </c>
+      <c r="C212" s="4" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J212" s="4" t="n">
+        <v>72.681</v>
+      </c>
+      <c r="K212" s="4" t="n">
+        <v>12.681</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="B213" s="6" t="n">
+        <v>199.189</v>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>-0.8110000000000001</v>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="J213" s="6" t="n">
+        <v>211.211</v>
+      </c>
+      <c r="K213" s="6" t="n">
+        <v>-13.789</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="I214" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J214" s="4" t="n">
+        <v>168.658</v>
+      </c>
+      <c r="K214" s="4" t="n">
+        <v>-1.342</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="I215" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J215" s="6" t="n">
+        <v>73.419</v>
+      </c>
+      <c r="K215" s="6" t="n">
+        <v>33.419</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="I216" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="J216" s="4" t="n">
+        <v>60.587</v>
+      </c>
+      <c r="K216" s="4" t="n">
+        <v>-1.413</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="I217" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="J217" s="6" t="n">
+        <v>105.006</v>
+      </c>
+      <c r="K217" s="6" t="n">
+        <v>30.006</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="I218" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="J218" s="4" t="n">
+        <v>148.566</v>
+      </c>
+      <c r="K218" s="4" t="n">
+        <v>38.566</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="I219" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="J219" s="6" t="n">
+        <v>100.236</v>
+      </c>
+      <c r="K219" s="6" t="n">
+        <v>-59.764</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="I220" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="J220" s="4" t="n">
+        <v>36.859</v>
+      </c>
+      <c r="K220" s="4" t="n">
+        <v>-49.141</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="I221" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="J221" s="6" t="n">
+        <v>55.926</v>
+      </c>
+      <c r="K221" s="6" t="n">
+        <v>12.926</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="I222" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="J222" s="4" t="n">
+        <v>62.005</v>
+      </c>
+      <c r="K222" s="4" t="n">
+        <v>30.005</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="I223" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="J223" s="6" t="n">
+        <v>68.926</v>
+      </c>
+      <c r="K223" s="6" t="n">
+        <v>-1.074</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="I224" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J224" s="4" t="n">
+        <v>120.622</v>
+      </c>
+      <c r="K224" s="4" t="n">
+        <v>60.622</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="I225" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="J225" s="6" t="n">
+        <v>184.872</v>
+      </c>
+      <c r="K225" s="6" t="n">
+        <v>-15.128</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="I226" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J226" s="4" t="n">
+        <v>119.506</v>
+      </c>
+      <c r="K226" s="4" t="n">
+        <v>69.506</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="I227" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J227" s="6" t="n">
+        <v>102.884</v>
+      </c>
+      <c r="K227" s="6" t="n">
+        <v>-47.116</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="I228" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J228" s="4" t="n">
+        <v>203.248</v>
+      </c>
+      <c r="K228" s="4" t="n">
+        <v>3.248</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="I229" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="J229" s="6" t="n">
+        <v>111.881</v>
+      </c>
+      <c r="K229" s="6" t="n">
+        <v>-43.119</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="I230" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>205.481</v>
+      </c>
+      <c r="K230" s="4" t="n">
+        <v>15.481</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="I231" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="J231" s="6" t="n">
+        <v>151.448</v>
+      </c>
+      <c r="K231" s="6" t="n">
+        <v>-68.55200000000001</v>
+      </c>
+    </row>
+    <row r="232"/>
+    <row r="233">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="n">
+        <v>1.8296</v>
+      </c>
+      <c r="C234" s="12" t="n">
+        <v>22.5871</v>
+      </c>
+      <c r="D234" s="12" t="n">
+        <v>19.0842</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="n">
+        <v>26.4155</v>
+      </c>
+      <c r="C235" s="11" t="n">
+        <v>1114.9666</v>
+      </c>
+      <c r="D235" s="11" t="n">
+        <v>774.4399</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="n">
+        <v>5.1396</v>
+      </c>
+      <c r="C236" s="12" t="n">
+        <v>33.3911</v>
+      </c>
+      <c r="D236" s="12" t="n">
+        <v>27.8288</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B237" s="11" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="C237" s="11" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="D237" s="11" t="n">
+        <v>0.9536</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>LMI</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C238" s="12" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="D238" s="12" t="n">
+        <v>0.7648</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>EAE</t>
+        </is>
+      </c>
+      <c r="B239" s="11" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="D239" s="11" t="n">
+        <v>0.1776</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
+        <is>
+          <t>VAF</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="n">
+        <v>99.8685</v>
+      </c>
+      <c r="C240" s="12" t="n">
+        <v>72.09350000000001</v>
+      </c>
+      <c r="D240" s="12" t="n">
+        <v>95.3644</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="7" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="B241" s="11" t="n">
+        <v>5.1392</v>
+      </c>
+      <c r="C241" s="11" t="n">
+        <v>33.3092</v>
+      </c>
+      <c r="D241" s="11" t="n">
+        <v>27.82</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
+    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A72:K72"/>
+    <mergeCell ref="E146:G146"/>
+    <mergeCell ref="I146:K146"/>
+    <mergeCell ref="A146:C146"/>
     <mergeCell ref="E73:G73"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="I73:K73"/>
@@ -32086,30 +37783,78 @@
           <t>Stacked Ensemble</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
-      <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
-      <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="12" t="n"/>
-      <c r="R55" s="12" t="n"/>
-      <c r="S55" s="12" t="n"/>
-      <c r="T55" s="12" t="n"/>
-      <c r="U55" s="12" t="n"/>
-      <c r="V55" s="12" t="n"/>
-      <c r="W55" s="12" t="n"/>
-      <c r="X55" s="12" t="n"/>
-      <c r="Y55" s="12" t="n"/>
+      <c r="B55" s="12" t="n">
+        <v>6.1798</v>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>76.42789999999999</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>8.7423</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0.9957</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>0.9268</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>99.5729</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>8.7143</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>27.7725</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>1548.3959</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>39.3497</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="P55" s="12" t="n">
+        <v>88.176</v>
+      </c>
+      <c r="Q55" s="12" t="n">
+        <v>39.2517</v>
+      </c>
+      <c r="R55" s="12" t="n">
+        <v>21.5545</v>
+      </c>
+      <c r="S55" s="12" t="n">
+        <v>946.5408</v>
+      </c>
+      <c r="T55" s="12" t="n">
+        <v>30.7659</v>
+      </c>
+      <c r="U55" s="12" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="V55" s="12" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+      <c r="W55" s="12" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="X55" s="12" t="n">
+        <v>94.33110000000001</v>
+      </c>
+      <c r="Y55" s="12" t="n">
+        <v>30.7648</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">

--- a/Slump_ML_Results_v2.xlsx
+++ b/Slump_ML_Results_v2.xlsx
@@ -80,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -102,11 +102,55 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +188,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,8 +578,11 @@
           <t>DATASET OVERVIEW — SLUMP DATA</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -859,7 +914,6 @@
         <v>129.9889</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
@@ -960,14 +1014,33 @@
           <t>SVR (RBF) — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -975,16 +1048,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1897,7 +1976,6 @@
         <v>2.308</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -2048,14 +2126,22 @@
         <v>153.2297</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2063,16 +2149,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -2158,7 +2250,7 @@
         <v>180</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>130</v>
@@ -2979,7 +3071,6 @@
         <v>-47.459</v>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
@@ -3130,14 +3221,22 @@
         <v>136.1385</v>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137"/>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="14" t="n"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
+      <c r="F138" s="14" t="n"/>
+      <c r="G138" s="14" t="n"/>
+      <c r="H138" s="14" t="n"/>
+      <c r="I138" s="14" t="n"/>
+      <c r="J138" s="14" t="n"/>
+      <c r="K138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3145,16 +3244,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="15" t="n"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F139" s="14" t="n"/>
+      <c r="G139" s="15" t="n"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J139" s="14" t="n"/>
+      <c r="K139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
@@ -4874,7 +4979,6 @@
         <v>-52.796</v>
       </c>
     </row>
-    <row r="225"/>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
@@ -5073,14 +5177,33 @@
           <t>ExtraTrees — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5088,16 +5211,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -6010,7 +6139,6 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -6161,14 +6289,22 @@
         <v>33.834</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6176,16 +6312,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -7106,7 +7248,6 @@
         <v>-14.759</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -7257,14 +7398,22 @@
         <v>25.6932</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7272,16 +7421,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -9001,7 +9156,6 @@
         <v>-62.379</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -9200,14 +9354,33 @@
           <t>HistGradientBoosting — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9215,16 +9388,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -10137,7 +10316,6 @@
         <v>-0.695</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -10288,14 +10466,22 @@
         <v>135.8788</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -10303,16 +10489,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -11223,7 +11415,6 @@
         <v>-49.127</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
@@ -11374,14 +11565,22 @@
         <v>173.2041</v>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -11389,16 +11588,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="15" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -13118,7 +13323,6 @@
         <v>-29.954</v>
       </c>
     </row>
-    <row r="227"/>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
@@ -13317,14 +13521,33 @@
           <t>Gaussian Process — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13332,16 +13555,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -14254,7 +14483,6 @@
         <v>2.607</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -14405,14 +14633,22 @@
         <v>54.2098</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -14420,16 +14656,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -15340,7 +15582,6 @@
         <v>0.012</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
@@ -15491,14 +15732,22 @@
         <v>89.91849999999999</v>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -15506,16 +15755,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="15" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -17235,7 +17490,6 @@
         <v>-57.127</v>
       </c>
     </row>
-    <row r="227"/>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
@@ -17434,14 +17688,33 @@
           <t>Stacked Ensemble — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -17449,16 +17722,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -18371,7 +18650,6 @@
         <v>0.969</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -18522,14 +18800,22 @@
         <v>65.34910000000001</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -18537,16 +18823,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -19457,7 +19749,6 @@
         <v>5.001</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
@@ -19608,14 +19899,22 @@
         <v>58.9637</v>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -19623,16 +19922,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="15" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -21352,7 +21657,6 @@
         <v>-53.507</v>
       </c>
     </row>
-    <row r="227"/>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
@@ -21551,14 +21855,33 @@
           <t>MLP (ANN) — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -21566,16 +21889,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -22488,7 +22817,6 @@
         <v>0.522</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -22639,14 +22967,22 @@
         <v>68.1644</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -22654,16 +22990,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -23570,7 +23912,6 @@
         <v>-46.518</v>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
@@ -23721,14 +24062,22 @@
         <v>132.7059</v>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137"/>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B138" s="14" t="n"/>
+      <c r="C138" s="14" t="n"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
+      <c r="F138" s="14" t="n"/>
+      <c r="G138" s="14" t="n"/>
+      <c r="H138" s="14" t="n"/>
+      <c r="I138" s="14" t="n"/>
+      <c r="J138" s="14" t="n"/>
+      <c r="K138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -23736,16 +24085,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B139" s="14" t="n"/>
+      <c r="C139" s="15" t="n"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F139" s="14" t="n"/>
+      <c r="G139" s="15" t="n"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J139" s="14" t="n"/>
+      <c r="K139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
@@ -25465,7 +25820,6 @@
         <v>-132.779</v>
       </c>
     </row>
-    <row r="225"/>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
@@ -25664,14 +26018,33 @@
           <t>BoostStack — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -25679,16 +26052,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -26601,7 +26980,6 @@
         <v>-7.496</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -26752,14 +27130,22 @@
         <v>37.1935</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -26767,16 +27153,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -27697,7 +28089,6 @@
         <v>-5.022</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -27848,14 +28239,22 @@
         <v>30.5827</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -27863,16 +28262,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -29592,7 +29997,6 @@
         <v>-71.938</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -29791,14 +30195,33 @@
           <t>GB_seed_ensemble — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -29806,16 +30229,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -30728,7 +31157,6 @@
         <v>1.191</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -30879,14 +31307,22 @@
         <v>24.41</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -30894,16 +31330,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -31824,7 +32266,6 @@
         <v>-0.231</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -31975,14 +32416,22 @@
         <v>33.27</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -31990,16 +32439,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -33719,7 +34174,6 @@
         <v>-68.55200000000001</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -33909,6 +34363,7 @@
           <t>METHODOLOGY</t>
         </is>
       </c>
+      <c r="B1" s="15" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -34081,6 +34536,31 @@
           <t>MODEL PERFORMANCE METRICS SUMMARY — SLUMP (CV-averaged)</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="14" t="n"/>
+      <c r="L1" s="14" t="n"/>
+      <c r="M1" s="14" t="n"/>
+      <c r="N1" s="14" t="n"/>
+      <c r="O1" s="14" t="n"/>
+      <c r="P1" s="14" t="n"/>
+      <c r="Q1" s="14" t="n"/>
+      <c r="R1" s="14" t="n"/>
+      <c r="S1" s="14" t="n"/>
+      <c r="T1" s="14" t="n"/>
+      <c r="U1" s="14" t="n"/>
+      <c r="V1" s="14" t="n"/>
+      <c r="W1" s="14" t="n"/>
+      <c r="X1" s="14" t="n"/>
+      <c r="Y1" s="14" t="n"/>
+      <c r="Z1" s="15" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -34089,6 +34569,31 @@
           <t>REGIME 1 — Random KFold (5 folds × 5 repeats, industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+      <c r="Z3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -34101,16 +34606,37 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="15" t="n"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="15" t="n"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="9" t="inlineStr">
@@ -35426,6 +35952,31 @@
           <t>REGIME 2 — GroupKFold strict (no mix-design leakage, honest)</t>
         </is>
       </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
+      <c r="T22" s="14" t="n"/>
+      <c r="U22" s="14" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="14" t="n"/>
+      <c r="X22" s="14" t="n"/>
+      <c r="Y22" s="14" t="n"/>
+      <c r="Z22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -35438,16 +35989,37 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="15" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="S23" s="14" t="n"/>
+      <c r="T23" s="14" t="n"/>
+      <c r="U23" s="14" t="n"/>
+      <c r="V23" s="14" t="n"/>
+      <c r="W23" s="14" t="n"/>
+      <c r="X23" s="14" t="n"/>
+      <c r="Y23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
@@ -36763,6 +37335,31 @@
           <t>REGIME 3 — LOOCV (Leave-One-Out, report-side high-R² protocol)</t>
         </is>
       </c>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14" t="n"/>
+      <c r="O41" s="14" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="n"/>
+      <c r="R41" s="14" t="n"/>
+      <c r="S41" s="14" t="n"/>
+      <c r="T41" s="14" t="n"/>
+      <c r="U41" s="14" t="n"/>
+      <c r="V41" s="14" t="n"/>
+      <c r="W41" s="14" t="n"/>
+      <c r="X41" s="14" t="n"/>
+      <c r="Y41" s="14" t="n"/>
+      <c r="Z41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -36775,16 +37372,37 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="15" t="n"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14" t="n"/>
+      <c r="O42" s="14" t="n"/>
+      <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="15" t="n"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="S42" s="14" t="n"/>
+      <c r="T42" s="14" t="n"/>
+      <c r="U42" s="14" t="n"/>
+      <c r="V42" s="14" t="n"/>
+      <c r="W42" s="14" t="n"/>
+      <c r="X42" s="14" t="n"/>
+      <c r="Y42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
@@ -37941,34 +38559,78 @@
           <t>BoostStack</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
-      <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="12" t="n"/>
-      <c r="R57" s="12" t="n"/>
-      <c r="S57" s="12" t="n"/>
-      <c r="T57" s="12" t="n"/>
-      <c r="U57" s="12" t="n">
-        <v>0.9448</v>
-      </c>
-      <c r="V57" s="12" t="n"/>
-      <c r="W57" s="12" t="n"/>
-      <c r="X57" s="12" t="n"/>
-      <c r="Y57" s="12" t="n"/>
+      <c r="B57" s="16" t="n">
+        <v>4.7124</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>7.1673</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>0.9442</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>99.7146</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>7.124</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>26.3888</v>
+      </c>
+      <c r="K57" s="16" t="n">
+        <v>1388.9275</v>
+      </c>
+      <c r="L57" s="16" t="n">
+        <v>37.2683</v>
+      </c>
+      <c r="M57" s="16" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="N57" s="16" t="n">
+        <v>0.6271</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>0.2371</v>
+      </c>
+      <c r="P57" s="16" t="n">
+        <v>89.355</v>
+      </c>
+      <c r="Q57" s="16" t="n">
+        <v>37.2434</v>
+      </c>
+      <c r="R57" s="16" t="n">
+        <v>21.4866</v>
+      </c>
+      <c r="S57" s="16" t="n">
+        <v>996.004</v>
+      </c>
+      <c r="T57" s="16" t="n">
+        <v>31.5595</v>
+      </c>
+      <c r="U57" s="16" t="n">
+        <v>0.9403</v>
+      </c>
+      <c r="V57" s="16" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="W57" s="16" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="X57" s="16" t="n">
+        <v>94.03830000000001</v>
+      </c>
+      <c r="Y57" s="16" t="n">
+        <v>31.5493</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -37976,34 +38638,78 @@
           <t>GB_seed_ensemble</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="11" t="n">
-        <v>0.9987</v>
-      </c>
-      <c r="F58" s="11" t="n"/>
-      <c r="G58" s="11" t="n"/>
-      <c r="H58" s="11" t="n"/>
-      <c r="I58" s="11" t="n"/>
-      <c r="J58" s="11" t="n"/>
-      <c r="K58" s="11" t="n"/>
-      <c r="L58" s="11" t="n"/>
-      <c r="M58" s="11" t="n"/>
-      <c r="N58" s="11" t="n"/>
-      <c r="O58" s="11" t="n"/>
-      <c r="P58" s="11" t="n"/>
-      <c r="Q58" s="11" t="n"/>
-      <c r="R58" s="11" t="n"/>
-      <c r="S58" s="11" t="n"/>
-      <c r="T58" s="11" t="n"/>
-      <c r="U58" s="11" t="n">
-        <v>0.9519</v>
-      </c>
-      <c r="V58" s="11" t="n"/>
-      <c r="W58" s="11" t="n"/>
-      <c r="X58" s="11" t="n"/>
-      <c r="Y58" s="11" t="n"/>
+      <c r="B58" s="17" t="n">
+        <v>1.2133</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>8.980700000000001</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>2.9968</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>99.9495</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>2.9967</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>24.2944</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>1293.7505</v>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>35.9687</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>0.9006999999999999</v>
+      </c>
+      <c r="N58" s="17" t="n">
+        <v>0.6567</v>
+      </c>
+      <c r="O58" s="17" t="n">
+        <v>0.2193</v>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>90.0767</v>
+      </c>
+      <c r="Q58" s="17" t="n">
+        <v>35.9588</v>
+      </c>
+      <c r="R58" s="17" t="n">
+        <v>19.0842</v>
+      </c>
+      <c r="S58" s="17" t="n">
+        <v>774.4399</v>
+      </c>
+      <c r="T58" s="17" t="n">
+        <v>27.8288</v>
+      </c>
+      <c r="U58" s="17" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="V58" s="17" t="n">
+        <v>0.7648</v>
+      </c>
+      <c r="W58" s="17" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="X58" s="17" t="n">
+        <v>95.3644</v>
+      </c>
+      <c r="Y58" s="17" t="n">
+        <v>27.82</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -38053,14 +38759,33 @@
           <t>Linear Regression — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -38068,16 +38793,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -38990,7 +39721,6 @@
         <v>57.443</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -39141,14 +39871,22 @@
         <v>50.9809</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -39156,16 +39894,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -40086,7 +40830,6 @@
         <v>-98.25</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -40237,14 +40980,22 @@
         <v>88.7732</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -40252,16 +41003,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -41981,7 +42738,6 @@
         <v>-126.266</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -42180,14 +42936,33 @@
           <t>Random Forest — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -42195,16 +42970,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -43117,7 +43898,6 @@
         <v>8.914</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -43268,14 +44048,22 @@
         <v>42.0112</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -43283,16 +44071,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -44213,7 +45007,6 @@
         <v>-26.704</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -44364,14 +45157,22 @@
         <v>30.3934</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -44379,16 +45180,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -46108,7 +46915,6 @@
         <v>-61.766</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -46307,14 +47113,33 @@
           <t>Gradient Boosting — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -46322,16 +47147,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -47244,7 +48075,6 @@
         <v>0.874</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -47395,14 +48225,22 @@
         <v>26.8788</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -47410,16 +48248,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -48340,7 +49184,6 @@
         <v>0.202</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -48491,14 +49334,22 @@
         <v>32.9876</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -48506,16 +49357,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -50235,7 +51092,6 @@
         <v>-79.69199999999999</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -50434,14 +51290,33 @@
           <t>AdaBoost — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -50449,16 +51324,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -51371,7 +52252,6 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -51522,14 +52402,22 @@
         <v>38.2844</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -51537,16 +52425,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -52467,7 +53361,6 @@
         <v>-2.2</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -52618,14 +53511,22 @@
         <v>33.9969</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -52633,16 +53534,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -54362,7 +55269,6 @@
         <v>-66.27800000000001</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
@@ -54561,14 +55467,33 @@
           <t>CatBoost — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -54576,16 +55501,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -54671,7 +55602,7 @@
         <v>173</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>220</v>
@@ -54700,7 +55631,7 @@
         <v>275</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>130</v>
@@ -54758,7 +55689,7 @@
         <v>75</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>145</v>
@@ -54903,7 +55834,7 @@
         <v>255</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>43</v>
@@ -54932,7 +55863,7 @@
         <v>285</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>620</v>
@@ -55079,7 +56010,7 @@
         <v>220</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>200</v>
@@ -55099,7 +56030,7 @@
         <v>580</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -55110,7 +56041,7 @@
         <v>165</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -55121,7 +56052,7 @@
         <v>120</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -55132,7 +56063,7 @@
         <v>190</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -55143,7 +56074,7 @@
         <v>130</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -55187,7 +56118,7 @@
         <v>155</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -55209,7 +56140,7 @@
         <v>205</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -55231,7 +56162,7 @@
         <v>144</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -55264,7 +56195,7 @@
         <v>185</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -55275,7 +56206,7 @@
         <v>225</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -55297,7 +56228,7 @@
         <v>70</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -55319,7 +56250,7 @@
         <v>195</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -55330,7 +56261,7 @@
         <v>175</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -55341,7 +56272,7 @@
         <v>200</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -55407,7 +56338,7 @@
         <v>86</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -55429,7 +56360,7 @@
         <v>190</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -55451,7 +56382,7 @@
         <v>62</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -55462,7 +56393,7 @@
         <v>650</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -55473,7 +56404,7 @@
         <v>150</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -55484,7 +56415,7 @@
         <v>160</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -55495,10 +56426,9 @@
         <v>210</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="60"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -55649,14 +56579,22 @@
         <v>32.3844</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -55664,16 +56602,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -55759,7 +56703,7 @@
         <v>160</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>210</v>
@@ -55817,7 +56761,7 @@
         <v>180</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E78" s="6" t="n">
         <v>155</v>
@@ -55875,7 +56819,7 @@
         <v>130</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>170</v>
@@ -55933,7 +56877,7 @@
         <v>190</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>185</v>
@@ -55991,7 +56935,7 @@
         <v>195</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>227</v>
@@ -56049,7 +56993,7 @@
         <v>205</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>200</v>
@@ -56107,7 +57051,7 @@
         <v>220</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>220</v>
@@ -56136,7 +57080,7 @@
         <v>120</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I89" s="4" t="n">
         <v>32</v>
@@ -56156,7 +57100,7 @@
         <v>124</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I90" s="6" t="n">
         <v>60</v>
@@ -56196,7 +57140,7 @@
         <v>140</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -56218,7 +57162,7 @@
         <v>620</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -56240,7 +57184,7 @@
         <v>550</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -56262,7 +57206,7 @@
         <v>620</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -56284,7 +57228,7 @@
         <v>200</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -56306,7 +57250,7 @@
         <v>290</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -56328,7 +57272,7 @@
         <v>275</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -56350,7 +57294,7 @@
         <v>185</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -56361,7 +57305,7 @@
         <v>130</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -56416,7 +57360,7 @@
         <v>173</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -56438,7 +57382,7 @@
         <v>145</v>
       </c>
       <c r="C114" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -56471,7 +57415,7 @@
         <v>75</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -56504,7 +57448,7 @@
         <v>40</v>
       </c>
       <c r="C120" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -56537,7 +57481,7 @@
         <v>160</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -56559,7 +57503,7 @@
         <v>50</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -56584,7 +57528,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
@@ -56735,14 +57678,22 @@
         <v>59.2266</v>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -56750,16 +57701,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="15" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -56816,7 +57773,7 @@
         <v>62</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E143" s="4" t="n">
         <v>220</v>
@@ -56990,7 +57947,7 @@
         <v>190</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E149" s="4" t="n">
         <v>175</v>
@@ -57019,7 +57976,7 @@
         <v>265</v>
       </c>
       <c r="C150" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>215</v>
@@ -57193,7 +58150,7 @@
         <v>165</v>
       </c>
       <c r="C156" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E156" s="6" t="n">
         <v>195</v>
@@ -57569,7 +58526,7 @@
         <v>180</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I173" s="4" t="n">
         <v>124</v>
@@ -57589,7 +58546,7 @@
         <v>130</v>
       </c>
       <c r="C174" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I174" s="6" t="n">
         <v>130</v>
@@ -57649,7 +58606,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I177" s="4" t="n">
         <v>620</v>
@@ -57749,7 +58706,7 @@
         <v>220</v>
       </c>
       <c r="C182" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I182" s="6" t="n">
         <v>580</v>
@@ -57769,7 +58726,7 @@
         <v>200</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I183" s="4" t="n">
         <v>175</v>
@@ -57789,7 +58746,7 @@
         <v>86</v>
       </c>
       <c r="C184" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I184" s="6" t="n">
         <v>200</v>
@@ -57829,7 +58786,7 @@
         <v>165</v>
       </c>
       <c r="C186" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I186" s="6" t="n">
         <v>290</v>
@@ -57849,7 +58806,7 @@
         <v>185</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I187" s="4" t="n">
         <v>285</v>
@@ -57909,7 +58866,7 @@
         <v>155</v>
       </c>
       <c r="C190" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I190" s="6" t="n">
         <v>220</v>
@@ -57929,7 +58886,7 @@
         <v>220</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I191" s="4" t="n">
         <v>185</v>
@@ -58009,7 +58966,7 @@
         <v>32</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I195" s="4" t="n">
         <v>150</v>
@@ -58049,7 +59006,7 @@
         <v>70</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I197" s="4" t="n">
         <v>227</v>
@@ -58069,7 +59026,7 @@
         <v>210</v>
       </c>
       <c r="C198" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I198" s="6" t="n">
         <v>223</v>
@@ -58209,7 +59166,7 @@
         <v>210</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I205" s="4" t="n">
         <v>80</v>
@@ -58479,7 +59436,6 @@
         <v>-49.702</v>
       </c>
     </row>
-    <row r="227"/>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
@@ -58678,14 +59634,33 @@
           <t>LightGBM — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -58693,16 +59668,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -59615,7 +60596,6 @@
         <v>-0.151</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -59766,14 +60746,22 @@
         <v>44.3775</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -59781,16 +60769,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -60701,7 +61695,6 @@
         <v>0.679</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
@@ -60852,14 +61845,22 @@
         <v>44.6089</v>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B140" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
+      <c r="G140" s="14" t="n"/>
+      <c r="H140" s="14" t="n"/>
+      <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -60867,16 +61868,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="15" t="n"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="15" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -62596,7 +63603,6 @@
         <v>-47.942</v>
       </c>
     </row>
-    <row r="227"/>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
@@ -62795,14 +63801,33 @@
           <t>XGBoost — Predictions vs Actual (representative fold per regime)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+      <c r="H1" s="14" t="n"/>
+      <c r="I1" s="14" t="n"/>
+      <c r="J1" s="14" t="n"/>
+      <c r="K1" s="15" t="n"/>
+    </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Random KFold (industry-comparable)</t>
         </is>
       </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -62810,16 +63835,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="15" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="15" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -63732,7 +64763,6 @@
         <v>0.283</v>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
@@ -63883,14 +64913,22 @@
         <v>35.3499</v>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>GroupKFold strict (honest)</t>
         </is>
       </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="14" t="n"/>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -63898,16 +64936,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B73" s="14" t="n"/>
+      <c r="C73" s="15" t="n"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F73" s="14" t="n"/>
+      <c r="G73" s="15" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -64828,7 +65872,6 @@
         <v>-0.618</v>
       </c>
     </row>
-    <row r="133"/>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
@@ -64979,14 +66022,22 @@
         <v>40.3414</v>
       </c>
     </row>
-    <row r="143"/>
-    <row r="144"/>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
           <t>LOOCV (Leave-One-Out — all 84 OOF predictions in Test column)</t>
         </is>
       </c>
+      <c r="B145" s="14" t="n"/>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
+      <c r="G145" s="14" t="n"/>
+      <c r="H145" s="14" t="n"/>
+      <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -64994,16 +66045,22 @@
           <t>Train</t>
         </is>
       </c>
+      <c r="B146" s="14" t="n"/>
+      <c r="C146" s="15" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Val</t>
         </is>
       </c>
+      <c r="F146" s="14" t="n"/>
+      <c r="G146" s="15" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -66723,7 +67780,6 @@
         <v>-74.387</v>
       </c>
     </row>
-    <row r="232"/>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
